--- a/data/Historical Data.xlsx
+++ b/data/Historical Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rahul\Documents\GitHub\mpg-commission-dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51D6A307-3E03-406F-9F62-53EEF9CF6DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{462B5180-12B2-48E0-8E3D-BE3DD18E5504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="674" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="251">
   <si>
     <t>Milk Procurement Historical Data- BIHAR</t>
   </si>
@@ -844,6 +844,15 @@
   </si>
   <si>
     <t>Overall Landed Cost</t>
+  </si>
+  <si>
+    <t>2016-17</t>
+  </si>
+  <si>
+    <t>2015-16</t>
+  </si>
+  <si>
+    <t>2014-15</t>
   </si>
 </sst>
 </file>
@@ -2519,19 +2528,10 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2558,6 +2558,12 @@
     <xf numFmtId="0" fontId="23" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2573,26 +2579,11 @@
     <xf numFmtId="0" fontId="28" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="16" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2639,6 +2630,57 @@
     <xf numFmtId="0" fontId="34" fillId="14" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="9" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="40" fillId="17" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -2665,39 +2707,6 @@
     </xf>
     <xf numFmtId="0" fontId="40" fillId="17" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="9" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -10246,34 +10255,43 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Volume Summary'!$B$4:$B$12</c:f>
+              <c:f>'Volume Summary'!$B$4:$B$15</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
+                  <c:v>2014-15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2015-16</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2016-17</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>2017-18</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="4">
                   <c:v>2018-19</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>2019-20</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>2020-21</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
                   <c:v>2021-22</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
                   <c:v>2022-23</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
                   <c:v>2023-24</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>2024-25</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="11">
                   <c:v>2025-26</c:v>
                 </c:pt>
               </c:strCache>
@@ -10281,35 +10299,44 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Volume Summary'!$C$4:$C$12</c:f>
+              <c:f>'Volume Summary'!$C$4:$C$15</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
+                  <c:v>28295.667260853417</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>27758.353495144074</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>29462.391682191785</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>63237.57688442072</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="4">
                   <c:v>95322.95081742006</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>78700.599993442622</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>85718.6394112329</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
                   <c:v>110324.2506682698</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
                   <c:v>137845.62607499998</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
                   <c:v>142133.71464057371</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>154571.97512891752</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="11">
                   <c:v>199773.05662250691</c:v>
                 </c:pt>
               </c:numCache>
@@ -10407,34 +10434,43 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Volume Summary'!$B$4:$B$12</c:f>
+              <c:f>'Volume Summary'!$B$4:$B$15</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
+                  <c:v>2014-15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2015-16</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2016-17</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>2017-18</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="4">
                   <c:v>2018-19</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>2019-20</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>2020-21</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
                   <c:v>2021-22</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
                   <c:v>2022-23</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
                   <c:v>2023-24</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>2024-25</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="11">
                   <c:v>2025-26</c:v>
                 </c:pt>
               </c:strCache>
@@ -10442,29 +10478,29 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Volume Summary'!$D$4:$D$12</c:f>
+              <c:f>'Volume Summary'!$D$4:$D$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
-                <c:pt idx="2" formatCode="0">
+                <c:ptCount val="12"/>
+                <c:pt idx="5" formatCode="0">
                   <c:v>30847.099248937458</c:v>
                 </c:pt>
-                <c:pt idx="3" formatCode="0">
+                <c:pt idx="6" formatCode="0">
                   <c:v>49747.200184759109</c:v>
                 </c:pt>
-                <c:pt idx="4" formatCode="0">
+                <c:pt idx="7" formatCode="0">
                   <c:v>54835.417665098968</c:v>
                 </c:pt>
-                <c:pt idx="5" formatCode="0">
+                <c:pt idx="8" formatCode="0">
                   <c:v>60401.683735536848</c:v>
                 </c:pt>
-                <c:pt idx="6" formatCode="0">
+                <c:pt idx="9" formatCode="0">
                   <c:v>63798.737846106502</c:v>
                 </c:pt>
-                <c:pt idx="7" formatCode="0">
+                <c:pt idx="10" formatCode="0">
                   <c:v>67664.380915753383</c:v>
                 </c:pt>
-                <c:pt idx="8" formatCode="0">
+                <c:pt idx="11" formatCode="0">
                   <c:v>93620.164875684859</c:v>
                 </c:pt>
               </c:numCache>
@@ -10559,34 +10595,43 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Volume Summary'!$B$4:$B$12</c:f>
+              <c:f>'Volume Summary'!$B$4:$B$15</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
+                  <c:v>2014-15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2015-16</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2016-17</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>2017-18</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="4">
                   <c:v>2018-19</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>2019-20</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>2020-21</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
                   <c:v>2021-22</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
                   <c:v>2022-23</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
                   <c:v>2023-24</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>2024-25</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="11">
                   <c:v>2025-26</c:v>
                 </c:pt>
               </c:strCache>
@@ -10594,17 +10639,17 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Volume Summary'!$E$4:$E$12</c:f>
+              <c:f>'Volume Summary'!$E$4:$E$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
-                <c:pt idx="6" formatCode="0">
+                <c:ptCount val="12"/>
+                <c:pt idx="9" formatCode="0">
                   <c:v>19848.561246683679</c:v>
                 </c:pt>
-                <c:pt idx="7" formatCode="0">
+                <c:pt idx="10" formatCode="0">
                   <c:v>32342.837311539719</c:v>
                 </c:pt>
-                <c:pt idx="8" formatCode="0">
+                <c:pt idx="11" formatCode="0">
                   <c:v>38794.674950972607</c:v>
                 </c:pt>
               </c:numCache>
@@ -10716,34 +10761,43 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Volume Summary'!$B$4:$B$12</c:f>
+              <c:f>'Volume Summary'!$B$4:$B$15</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
+                  <c:v>2014-15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2015-16</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2016-17</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>2017-18</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="4">
                   <c:v>2018-19</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>2019-20</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>2020-21</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
                   <c:v>2021-22</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
                   <c:v>2022-23</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
                   <c:v>2023-24</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>2024-25</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="11">
                   <c:v>2025-26</c:v>
                 </c:pt>
               </c:strCache>
@@ -10751,35 +10805,44 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Volume Summary'!$F$4:$F$12</c:f>
+              <c:f>'Volume Summary'!$F$4:$F$15</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
+                  <c:v>28295.667260853417</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>27758.353495144074</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>29462.391682191785</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>63237.57688442072</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="4">
                   <c:v>95322.95081742006</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>109547.69924238008</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>135465.839595992</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
                   <c:v>165159.66833336878</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
                   <c:v>198247.30981053683</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
                   <c:v>225781.01373336388</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>254579.19335621063</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="11">
                   <c:v>332187.89644916437</c:v>
                 </c:pt>
               </c:numCache>
@@ -18848,13 +18911,13 @@
     <xdr:from>
       <xdr:col>15</xdr:col>
       <xdr:colOff>441324</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>174625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>34924</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -19661,18 +19724,18 @@
     <row r="41" spans="3:11" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="42" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C42" s="200"/>
-      <c r="D42" s="222" t="s">
+      <c r="D42" s="221" t="s">
         <v>228</v>
       </c>
-      <c r="E42" s="222"/>
-      <c r="F42" s="222"/>
-      <c r="G42" s="222"/>
-      <c r="H42" s="222" t="s">
+      <c r="E42" s="221"/>
+      <c r="F42" s="221"/>
+      <c r="G42" s="221"/>
+      <c r="H42" s="221" t="s">
         <v>222</v>
       </c>
-      <c r="I42" s="222"/>
-      <c r="J42" s="222"/>
-      <c r="K42" s="222"/>
+      <c r="I42" s="221"/>
+      <c r="J42" s="221"/>
+      <c r="K42" s="221"/>
     </row>
     <row r="43" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C43" s="100" t="s">
@@ -20108,12 +20171,12 @@
       </c>
     </row>
     <row r="72" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C72" s="223" t="s">
+      <c r="C72" s="222" t="s">
         <v>232</v>
       </c>
-      <c r="D72" s="223"/>
-      <c r="E72" s="223"/>
-      <c r="F72" s="223"/>
+      <c r="D72" s="222"/>
+      <c r="E72" s="222"/>
+      <c r="F72" s="222"/>
     </row>
     <row r="73" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C73" s="100" t="s">
@@ -20221,41 +20284,41 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C3" s="261" t="s">
+      <c r="C3" s="272" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="261" t="s">
+      <c r="D3" s="272" t="s">
         <v>61</v>
       </c>
-      <c r="E3" s="261" t="s">
+      <c r="E3" s="272" t="s">
         <v>52</v>
       </c>
-      <c r="F3" s="263" t="s">
+      <c r="F3" s="274" t="s">
         <v>94</v>
       </c>
-      <c r="G3" s="264"/>
-      <c r="H3" s="266" t="s">
+      <c r="G3" s="275"/>
+      <c r="H3" s="277" t="s">
         <v>187</v>
       </c>
-      <c r="I3" s="267"/>
-      <c r="J3" s="261" t="s">
+      <c r="I3" s="278"/>
+      <c r="J3" s="272" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="4" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C4" s="265"/>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="263" t="s">
+      <c r="C4" s="276"/>
+      <c r="D4" s="273"/>
+      <c r="E4" s="273"/>
+      <c r="F4" s="274" t="s">
         <v>186</v>
       </c>
-      <c r="G4" s="264"/>
-      <c r="H4" s="268"/>
-      <c r="I4" s="269"/>
-      <c r="J4" s="262"/>
+      <c r="G4" s="275"/>
+      <c r="H4" s="279"/>
+      <c r="I4" s="280"/>
+      <c r="J4" s="273"/>
     </row>
     <row r="5" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C5" s="262"/>
+      <c r="C5" s="273"/>
       <c r="D5" s="144" t="s">
         <v>93</v>
       </c>
@@ -20662,54 +20725,54 @@
       </c>
     </row>
     <row r="21" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="271" t="s">
+      <c r="C21" s="266" t="s">
         <v>161</v>
       </c>
-      <c r="D21" s="271"/>
-      <c r="E21" s="271"/>
-      <c r="F21" s="271"/>
-      <c r="G21" s="271"/>
-      <c r="H21" s="271"/>
+      <c r="D21" s="266"/>
+      <c r="E21" s="266"/>
+      <c r="F21" s="266"/>
+      <c r="G21" s="266"/>
+      <c r="H21" s="266"/>
     </row>
     <row r="22" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C22" s="272" t="s">
+      <c r="C22" s="267" t="s">
         <v>188</v>
       </c>
-      <c r="D22" s="273"/>
-      <c r="E22" s="273"/>
-      <c r="F22" s="273"/>
-      <c r="G22" s="273"/>
-      <c r="H22" s="274"/>
+      <c r="D22" s="268"/>
+      <c r="E22" s="268"/>
+      <c r="F22" s="268"/>
+      <c r="G22" s="268"/>
+      <c r="H22" s="269"/>
     </row>
     <row r="23" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C23" s="275" t="s">
+      <c r="C23" s="270" t="s">
         <v>162</v>
       </c>
-      <c r="D23" s="276" t="s">
+      <c r="D23" s="271" t="s">
         <v>163</v>
       </c>
-      <c r="E23" s="276" t="s">
+      <c r="E23" s="271" t="s">
         <v>163</v>
       </c>
       <c r="F23" s="150" t="s">
         <v>164</v>
       </c>
-      <c r="G23" s="276" t="s">
+      <c r="G23" s="271" t="s">
         <v>164</v>
       </c>
-      <c r="H23" s="276"/>
+      <c r="H23" s="271"/>
     </row>
     <row r="24" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C24" s="275"/>
-      <c r="D24" s="276"/>
-      <c r="E24" s="276"/>
+      <c r="C24" s="270"/>
+      <c r="D24" s="271"/>
+      <c r="E24" s="271"/>
       <c r="F24" s="150" t="s">
         <v>165</v>
       </c>
-      <c r="G24" s="276" t="s">
+      <c r="G24" s="271" t="s">
         <v>166</v>
       </c>
-      <c r="H24" s="276"/>
+      <c r="H24" s="271"/>
     </row>
     <row r="25" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C25" s="151" t="s">
@@ -20725,10 +20788,10 @@
       <c r="F25" s="153">
         <v>50000</v>
       </c>
-      <c r="G25" s="270">
+      <c r="G25" s="264">
         <v>30000</v>
       </c>
-      <c r="H25" s="270"/>
+      <c r="H25" s="264"/>
     </row>
     <row r="26" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C26" s="151" t="s">
@@ -20744,10 +20807,10 @@
       <c r="F26" s="153">
         <v>37.18</v>
       </c>
-      <c r="G26" s="270">
+      <c r="G26" s="264">
         <v>37.18</v>
       </c>
-      <c r="H26" s="270"/>
+      <c r="H26" s="264"/>
     </row>
     <row r="27" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C27" s="151" t="s">
@@ -20763,10 +20826,10 @@
       <c r="F27" s="153">
         <v>3.11</v>
       </c>
-      <c r="G27" s="270">
+      <c r="G27" s="264">
         <v>3</v>
       </c>
-      <c r="H27" s="270"/>
+      <c r="H27" s="264"/>
     </row>
     <row r="28" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C28" s="151" t="s">
@@ -20781,10 +20844,10 @@
       <c r="F28" s="153">
         <v>1.1200000000000001</v>
       </c>
-      <c r="G28" s="270">
+      <c r="G28" s="264">
         <v>1.1200000000000001</v>
       </c>
-      <c r="H28" s="270"/>
+      <c r="H28" s="264"/>
     </row>
     <row r="29" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C29" s="151" t="s">
@@ -20800,10 +20863,10 @@
       <c r="F29" s="153">
         <v>0.92</v>
       </c>
-      <c r="G29" s="270">
+      <c r="G29" s="264">
         <v>1</v>
       </c>
-      <c r="H29" s="270"/>
+      <c r="H29" s="264"/>
     </row>
     <row r="30" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C30" s="151" t="s">
@@ -20819,10 +20882,10 @@
       <c r="F30" s="153">
         <v>0.88</v>
       </c>
-      <c r="G30" s="270">
+      <c r="G30" s="264">
         <v>0.5</v>
       </c>
-      <c r="H30" s="270"/>
+      <c r="H30" s="264"/>
     </row>
     <row r="31" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C31" s="151" t="s">
@@ -20838,10 +20901,10 @@
       <c r="F31" s="153">
         <v>0.56000000000000005</v>
       </c>
-      <c r="G31" s="270">
+      <c r="G31" s="264">
         <v>1</v>
       </c>
-      <c r="H31" s="270"/>
+      <c r="H31" s="264"/>
     </row>
     <row r="32" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C32" s="151" t="s">
@@ -20857,10 +20920,10 @@
       <c r="F32" s="153">
         <v>0.61</v>
       </c>
-      <c r="G32" s="270">
+      <c r="G32" s="264">
         <v>0.5</v>
       </c>
-      <c r="H32" s="270"/>
+      <c r="H32" s="264"/>
     </row>
     <row r="33" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C33" s="151" t="s">
@@ -20876,10 +20939,10 @@
       <c r="F33" s="153">
         <v>0.14000000000000001</v>
       </c>
-      <c r="G33" s="270">
+      <c r="G33" s="264">
         <v>0</v>
       </c>
-      <c r="H33" s="270"/>
+      <c r="H33" s="264"/>
     </row>
     <row r="34" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C34" s="151" t="s">
@@ -20894,10 +20957,10 @@
       <c r="F34" s="153">
         <v>0.7</v>
       </c>
-      <c r="G34" s="270">
+      <c r="G34" s="264">
         <v>0</v>
       </c>
-      <c r="H34" s="270"/>
+      <c r="H34" s="264"/>
     </row>
     <row r="35" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C35" s="151" t="s">
@@ -20912,10 +20975,10 @@
       <c r="F35" s="153">
         <v>1.6</v>
       </c>
-      <c r="G35" s="270">
+      <c r="G35" s="264">
         <v>0</v>
       </c>
-      <c r="H35" s="270"/>
+      <c r="H35" s="264"/>
     </row>
     <row r="36" spans="3:8" ht="30" x14ac:dyDescent="0.25">
       <c r="C36" s="154" t="s">
@@ -20931,10 +20994,10 @@
       <c r="F36" s="156">
         <v>43.71</v>
       </c>
-      <c r="G36" s="280">
+      <c r="G36" s="265">
         <v>41.3</v>
       </c>
-      <c r="H36" s="280"/>
+      <c r="H36" s="265"/>
     </row>
     <row r="37" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C37" s="151" t="s">
@@ -20946,11 +21009,11 @@
       <c r="E37" s="152">
         <v>42.11</v>
       </c>
-      <c r="F37" s="277" t="s">
+      <c r="F37" s="261" t="s">
         <v>178</v>
       </c>
-      <c r="G37" s="277"/>
-      <c r="H37" s="277"/>
+      <c r="G37" s="261"/>
+      <c r="H37" s="261"/>
     </row>
     <row r="38" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C38" s="151" t="s">
@@ -20963,9 +21026,9 @@
       <c r="E38" s="152">
         <v>40.090000000000003</v>
       </c>
-      <c r="F38" s="277"/>
-      <c r="G38" s="277"/>
-      <c r="H38" s="277"/>
+      <c r="F38" s="261"/>
+      <c r="G38" s="261"/>
+      <c r="H38" s="261"/>
     </row>
     <row r="39" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C39" s="151" t="s">
@@ -20978,9 +21041,9 @@
       <c r="E39" s="152">
         <v>37.69</v>
       </c>
-      <c r="F39" s="277"/>
-      <c r="G39" s="277"/>
-      <c r="H39" s="277"/>
+      <c r="F39" s="261"/>
+      <c r="G39" s="261"/>
+      <c r="H39" s="261"/>
     </row>
     <row r="40" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C40" s="157" t="s">
@@ -20993,11 +21056,11 @@
       <c r="E40" s="155">
         <v>40.15</v>
       </c>
-      <c r="F40" s="278">
+      <c r="F40" s="262">
         <v>42.8</v>
       </c>
-      <c r="G40" s="278"/>
-      <c r="H40" s="278"/>
+      <c r="G40" s="262"/>
+      <c r="H40" s="262"/>
     </row>
     <row r="41" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C41" s="158" t="s">
@@ -21009,21 +21072,19 @@
       <c r="E41" s="159" t="s">
         <v>183</v>
       </c>
-      <c r="F41" s="279"/>
-      <c r="G41" s="279"/>
+      <c r="F41" s="263"/>
+      <c r="G41" s="263"/>
       <c r="H41" s="160"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="F37:H39"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I4"/>
     <mergeCell ref="G30:H30"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="C22:H22"/>
@@ -21037,13 +21098,15 @@
     <mergeCell ref="G27:H27"/>
     <mergeCell ref="G28:H28"/>
     <mergeCell ref="G29:H29"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I4"/>
+    <mergeCell ref="F37:H39"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G36:H36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -21055,7 +21118,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="B3:U36"/>
+  <dimension ref="B3:U39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.42578125" bestFit="1" customWidth="1"/>
@@ -21092,632 +21155,686 @@
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="82" t="s">
-        <v>67</v>
+        <v>250</v>
       </c>
       <c r="C4" s="51">
-        <f>BIHAR!U40</f>
-        <v>63237.57688442072</v>
+        <f>BIHAR!U35</f>
+        <v>28295.667260853417</v>
       </c>
       <c r="D4" s="82"/>
       <c r="E4" s="82"/>
       <c r="F4" s="51">
-        <f>C4+D4+E4</f>
-        <v>63237.57688442072</v>
+        <f t="shared" ref="F4:F6" si="0">C4+D4+E4</f>
+        <v>28295.667260853417</v>
       </c>
       <c r="G4" s="60">
         <v>1</v>
       </c>
-      <c r="H4" s="86"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="82" t="s">
-        <v>68</v>
+        <v>249</v>
       </c>
       <c r="C5" s="51">
-        <f>BIHAR!U42</f>
-        <v>95322.95081742006</v>
+        <f>BIHAR!U37</f>
+        <v>27758.353495144074</v>
       </c>
       <c r="D5" s="82"/>
       <c r="E5" s="82"/>
       <c r="F5" s="51">
-        <f t="shared" ref="F5:F10" si="0">C5+D5+E5</f>
-        <v>95322.95081742006</v>
+        <f t="shared" si="0"/>
+        <v>27758.353495144074</v>
       </c>
       <c r="G5" s="60">
-        <f t="shared" ref="G5:G10" si="1">F5/F4</f>
-        <v>1.5073782948964309</v>
-      </c>
-      <c r="H5" s="86"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="82" t="s">
+        <v>248</v>
+      </c>
+      <c r="C6" s="51">
+        <f>BIHAR!U39</f>
+        <v>29462.391682191785</v>
+      </c>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="51">
+        <f t="shared" si="0"/>
+        <v>29462.391682191785</v>
+      </c>
+      <c r="G6" s="60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="82" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="51">
+        <f>BIHAR!U41</f>
+        <v>63237.57688442072</v>
+      </c>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="51">
+        <f>C7+D7+E7</f>
+        <v>63237.57688442072</v>
+      </c>
+      <c r="G7" s="60">
+        <v>1</v>
+      </c>
+      <c r="H7" s="86"/>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="82" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="51">
+        <f>BIHAR!U42</f>
+        <v>95322.95081742006</v>
+      </c>
+      <c r="D8" s="82"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="51">
+        <f t="shared" ref="F8:F13" si="1">C8+D8+E8</f>
+        <v>95322.95081742006</v>
+      </c>
+      <c r="G8" s="60">
+        <f t="shared" ref="G8:G13" si="2">F8/F7</f>
+        <v>1.5073782948964309</v>
+      </c>
+      <c r="H8" s="86"/>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="82" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="51">
+      <c r="C9" s="51">
         <f>BIHAR!U45</f>
         <v>78700.599993442622</v>
       </c>
-      <c r="D6" s="51">
+      <c r="D9" s="51">
         <f>'WEST BENGAL'!U26</f>
         <v>30847.099248937458</v>
       </c>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51">
-        <f t="shared" si="0"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51">
+        <f t="shared" si="1"/>
         <v>109547.69924238008</v>
       </c>
-      <c r="G6" s="60">
-        <f t="shared" si="1"/>
+      <c r="G9" s="60">
+        <f t="shared" si="2"/>
         <v>1.1492268997442794</v>
       </c>
-      <c r="H6" s="86"/>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="82" t="s">
+      <c r="H9" s="86"/>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="82" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="51">
+      <c r="C10" s="51">
         <f>BIHAR!U49</f>
         <v>85718.6394112329</v>
       </c>
-      <c r="D7" s="51">
+      <c r="D10" s="51">
         <f>'WEST BENGAL'!U29</f>
         <v>49747.200184759109</v>
       </c>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51">
-        <f t="shared" si="0"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51">
+        <f t="shared" si="1"/>
         <v>135465.839595992</v>
       </c>
-      <c r="G7" s="60">
-        <f t="shared" si="1"/>
+      <c r="G10" s="60">
+        <f t="shared" si="2"/>
         <v>1.2365922838440144</v>
       </c>
-      <c r="H7" s="86"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="82" t="s">
+      <c r="H10" s="86"/>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="82" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="51">
+      <c r="C11" s="51">
         <f>BIHAR!U53</f>
         <v>110324.2506682698</v>
       </c>
-      <c r="D8" s="51">
+      <c r="D11" s="51">
         <f>'WEST BENGAL'!U33</f>
         <v>54835.417665098968</v>
       </c>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51">
-        <f t="shared" si="0"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51">
+        <f t="shared" si="1"/>
         <v>165159.66833336878</v>
       </c>
-      <c r="G8" s="60">
-        <f t="shared" si="1"/>
+      <c r="G11" s="60">
+        <f t="shared" si="2"/>
         <v>1.2191979086826206</v>
       </c>
-      <c r="H8" s="86"/>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="82" t="s">
+      <c r="H11" s="86"/>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B12" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="51">
+      <c r="C12" s="51">
         <f>BIHAR!U58</f>
         <v>137845.62607499998</v>
       </c>
-      <c r="D9" s="51">
+      <c r="D12" s="51">
         <f>'WEST BENGAL'!U37</f>
         <v>60401.683735536848</v>
       </c>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51">
-        <f t="shared" si="0"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51">
+        <f t="shared" si="1"/>
         <v>198247.30981053683</v>
       </c>
-      <c r="G9" s="60">
-        <f t="shared" si="1"/>
+      <c r="G12" s="60">
+        <f t="shared" si="2"/>
         <v>1.2003372966963208</v>
       </c>
-      <c r="H9" s="86"/>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="82" t="s">
+      <c r="H12" s="86"/>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="82" t="s">
         <v>93</v>
       </c>
-      <c r="C10" s="51">
+      <c r="C13" s="51">
         <f>BIHAR!U63</f>
         <v>142133.71464057371</v>
       </c>
-      <c r="D10" s="51">
+      <c r="D13" s="51">
         <f>'WEST BENGAL'!U41</f>
         <v>63798.737846106502</v>
       </c>
-      <c r="E10" s="51">
+      <c r="E13" s="51">
         <f>JHARKHAND!U19</f>
         <v>19848.561246683679</v>
       </c>
-      <c r="F10" s="51">
-        <f t="shared" si="0"/>
+      <c r="F13" s="51">
+        <f t="shared" si="1"/>
         <v>225781.01373336388</v>
       </c>
-      <c r="G10" s="60">
-        <f t="shared" si="1"/>
+      <c r="G13" s="60">
+        <f t="shared" si="2"/>
         <v>1.13888563708199</v>
       </c>
-      <c r="H10" s="86"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="82" t="s">
+      <c r="H13" s="86"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="82" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="51">
+      <c r="C14" s="51">
         <f>BIHAR!U68</f>
         <v>154571.97512891752</v>
       </c>
-      <c r="D11" s="51">
+      <c r="D14" s="51">
         <f>'WEST BENGAL'!U45</f>
         <v>67664.380915753383</v>
       </c>
-      <c r="E11" s="51">
+      <c r="E14" s="51">
         <f>JHARKHAND!U24</f>
         <v>32342.837311539719</v>
       </c>
-      <c r="F11" s="51">
-        <f>C11+D11+E11</f>
+      <c r="F14" s="51">
+        <f>C14+D14+E14</f>
         <v>254579.19335621063</v>
       </c>
-      <c r="G11" s="60">
-        <f>F11/F10</f>
+      <c r="G14" s="60">
+        <f>F14/F13</f>
         <v>1.1275491643281217</v>
       </c>
-      <c r="H11" s="86"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="82" t="s">
+      <c r="H14" s="86"/>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="82" t="s">
         <v>237</v>
       </c>
-      <c r="C12" s="51">
+      <c r="C15" s="51">
         <f>BIHAR!U73</f>
         <v>199773.05662250691</v>
       </c>
-      <c r="D12" s="51">
+      <c r="D15" s="51">
         <f>'WEST BENGAL'!U49</f>
         <v>93620.164875684859</v>
       </c>
-      <c r="E12" s="51">
+      <c r="E15" s="51">
         <f>JHARKHAND!U29</f>
         <v>38794.674950972607</v>
       </c>
-      <c r="F12" s="51">
-        <f>C12+D12+E12</f>
+      <c r="F15" s="51">
+        <f>C15+D15+E15</f>
         <v>332187.89644916437</v>
       </c>
-      <c r="G12" s="60">
-        <f>F12/F11</f>
+      <c r="G15" s="60">
+        <f>F15/F14</f>
         <v>1.3048509270133581</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="185" t="s">
+    <row r="18" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="185" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="185" t="s">
+      <c r="C19" s="185" t="s">
         <v>200</v>
       </c>
-      <c r="D16" s="185" t="s">
+      <c r="D19" s="185" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="185" t="s">
+      <c r="E19" s="185" t="s">
         <v>100</v>
       </c>
-      <c r="F16" s="185" t="s">
+      <c r="F19" s="185" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="186" t="s">
+    <row r="20" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="186" t="s">
         <v>201</v>
       </c>
-      <c r="C17" s="187" t="s">
+      <c r="C20" s="187" t="s">
         <v>202</v>
       </c>
-      <c r="D17" s="189">
+      <c r="D20" s="189">
         <f>BIHAR!P14+'WEST BENGAL'!V9+JHARKHAND!N4</f>
         <v>896</v>
       </c>
-      <c r="E17" s="189">
+      <c r="E20" s="189">
         <f>BIHAR!P15+'WEST BENGAL'!V10+JHARKHAND!O5</f>
         <v>1038</v>
       </c>
-      <c r="F17" s="189">
+      <c r="F20" s="189">
         <f>BIHAR!P16+'WEST BENGAL'!V11+JHARKHAND!H6</f>
         <v>1452</v>
       </c>
     </row>
-    <row r="18" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="186" t="s">
+    <row r="21" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="186" t="s">
         <v>203</v>
       </c>
-      <c r="C18" s="187" t="s">
+      <c r="C21" s="187" t="s">
         <v>204</v>
       </c>
-      <c r="D18" s="189">
+      <c r="D21" s="189">
         <f>BIHAR!U59+'WEST BENGAL'!U38+JHARKHAND!U15</f>
         <v>179667.80940119404</v>
       </c>
-      <c r="E18" s="189">
+      <c r="E21" s="189">
         <f>BIHAR!U64+'WEST BENGAL'!U42+JHARKHAND!U20</f>
         <v>175614.2399997038</v>
       </c>
-      <c r="F18" s="189">
+      <c r="F21" s="189">
         <f>BIHAR!U69+'WEST BENGAL'!U46+JHARKHAND!U25</f>
         <v>227179.33010190408</v>
       </c>
     </row>
-    <row r="19" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="186" t="s">
+    <row r="22" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="186" t="s">
         <v>205</v>
       </c>
-      <c r="C19" s="187" t="s">
+      <c r="C22" s="187" t="s">
         <v>202</v>
       </c>
-      <c r="D19" s="189">
+      <c r="D22" s="189">
         <f>BIHAR!P28+'WEST BENGAL'!V18+JHARKHAND!O9</f>
         <v>20828</v>
       </c>
-      <c r="E19" s="189">
+      <c r="E22" s="189">
         <f>BIHAR!P29+'WEST BENGAL'!V19+JHARKHAND!O10</f>
         <v>14119</v>
       </c>
-      <c r="F19" s="189">
+      <c r="F22" s="189">
         <f>BIHAR!D30+'WEST BENGAL'!E20+JHARKHAND!H11</f>
         <v>12935</v>
       </c>
     </row>
-    <row r="20" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="186" t="s">
+    <row r="23" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="186" t="s">
         <v>206</v>
       </c>
-      <c r="C20" s="187" t="s">
+      <c r="C23" s="187" t="s">
         <v>202</v>
       </c>
-      <c r="D20" s="191">
+      <c r="D23" s="191">
         <f>13+1+10</f>
         <v>24</v>
       </c>
-      <c r="E20" s="191">
+      <c r="E23" s="191">
         <f>14+1+7</f>
         <v>22</v>
       </c>
-      <c r="F20" s="191">
+      <c r="F23" s="191">
         <f>18+2+11</f>
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="186" t="s">
+    <row r="24" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="186" t="s">
         <v>207</v>
       </c>
-      <c r="C21" s="187" t="s">
+      <c r="C24" s="187" t="s">
         <v>208</v>
       </c>
-      <c r="D21" s="191">
+      <c r="D24" s="191">
         <f>93+80+5</f>
         <v>178</v>
       </c>
-      <c r="E21" s="191">
+      <c r="E24" s="191">
         <f>110+5+62</f>
         <v>177</v>
       </c>
-      <c r="F21" s="191">
+      <c r="F24" s="191">
         <f>125+82+10</f>
         <v>217</v>
       </c>
     </row>
-    <row r="22" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="186" t="s">
+    <row r="25" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="186" t="s">
         <v>209</v>
       </c>
-      <c r="C22" s="188"/>
-      <c r="D22" s="192">
+      <c r="C25" s="188"/>
+      <c r="D25" s="192">
         <v>0.66</v>
       </c>
-      <c r="E22" s="192">
+      <c r="E25" s="192">
         <v>0.7</v>
       </c>
-      <c r="F22" s="192">
+      <c r="F25" s="192">
         <v>0.68</v>
       </c>
     </row>
-    <row r="23" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="186" t="s">
+    <row r="26" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="186" t="s">
         <v>210</v>
       </c>
-      <c r="C23" s="187" t="s">
+      <c r="C26" s="187" t="s">
         <v>208</v>
       </c>
-      <c r="D23" s="191">
+      <c r="D26" s="191">
         <f>39+4+10</f>
         <v>53</v>
       </c>
-      <c r="E23" s="191">
+      <c r="E26" s="191">
         <f>29+8.5+29</f>
         <v>66.5</v>
       </c>
-      <c r="F23" s="191">
+      <c r="F26" s="191">
         <f>32+11+22</f>
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="186" t="s">
+    <row r="27" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="186" t="s">
         <v>211</v>
       </c>
-      <c r="C24" s="188"/>
-      <c r="D24" s="192">
+      <c r="C27" s="188"/>
+      <c r="D27" s="192">
         <v>0.65</v>
       </c>
-      <c r="E24" s="192">
+      <c r="E27" s="192">
         <v>0.44</v>
       </c>
-      <c r="F24" s="192">
+      <c r="F27" s="192">
         <v>0.72</v>
       </c>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B29" s="175" t="s">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B32" s="175" t="s">
         <v>66</v>
       </c>
-      <c r="C29" s="175" t="s">
+      <c r="C32" s="175" t="s">
         <v>70</v>
       </c>
-      <c r="D29" s="175" t="s">
+      <c r="D32" s="175" t="s">
         <v>71</v>
       </c>
-      <c r="E29" s="175" t="s">
+      <c r="E32" s="175" t="s">
         <v>72</v>
       </c>
-      <c r="F29" s="175" t="s">
+      <c r="F32" s="175" t="s">
         <v>93</v>
       </c>
-      <c r="G29" s="175" t="s">
+      <c r="G32" s="175" t="s">
         <v>94</v>
       </c>
-      <c r="H29" s="175" t="s">
+      <c r="H32" s="175" t="s">
         <v>237</v>
       </c>
-      <c r="I29" s="175" t="s">
+      <c r="I32" s="175" t="s">
         <v>239</v>
       </c>
-      <c r="J29" s="175" t="s">
+      <c r="J32" s="175" t="s">
         <v>240</v>
       </c>
-      <c r="K29" s="175" t="s">
+      <c r="K32" s="175" t="s">
         <v>241</v>
       </c>
-      <c r="L29" s="175" t="s">
+      <c r="L32" s="175" t="s">
         <v>242</v>
       </c>
-      <c r="M29" s="175" t="s">
+      <c r="M32" s="175" t="s">
         <v>243</v>
       </c>
-      <c r="N29" s="175" t="s">
+      <c r="N32" s="175" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B30" s="82" t="s">
-        <v>194</v>
-      </c>
-      <c r="C30" s="82">
-        <v>2</v>
-      </c>
-      <c r="D30" s="82">
-        <v>2</v>
-      </c>
-      <c r="E30" s="82">
-        <v>2</v>
-      </c>
-      <c r="F30" s="82">
-        <v>3</v>
-      </c>
-      <c r="G30" s="82">
-        <v>3</v>
-      </c>
-      <c r="H30" s="82">
-        <v>3</v>
-      </c>
-      <c r="I30" s="82">
-        <v>3</v>
-      </c>
-      <c r="J30" s="82">
-        <v>3</v>
-      </c>
-      <c r="K30" s="82">
-        <v>3</v>
-      </c>
-      <c r="L30" s="82">
-        <v>3</v>
-      </c>
-      <c r="M30" s="82">
-        <v>3</v>
-      </c>
-      <c r="N30" s="82">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B31" s="82" t="s">
-        <v>197</v>
-      </c>
-      <c r="C31" s="220">
-        <v>9</v>
-      </c>
-      <c r="D31" s="220">
-        <v>10</v>
-      </c>
-      <c r="E31" s="220">
-        <v>11</v>
-      </c>
-      <c r="F31" s="220">
-        <v>12</v>
-      </c>
-      <c r="G31" s="220">
-        <v>13</v>
-      </c>
-      <c r="H31" s="82"/>
-      <c r="I31" s="82"/>
-      <c r="J31" s="82"/>
-      <c r="K31" s="82"/>
-      <c r="L31" s="82"/>
-      <c r="M31" s="82"/>
-      <c r="N31" s="82"/>
-    </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B32" s="82" t="s">
-        <v>238</v>
-      </c>
-      <c r="C32" s="220">
-        <v>2</v>
-      </c>
-      <c r="D32" s="220">
-        <v>3</v>
-      </c>
-      <c r="E32" s="220">
-        <v>3</v>
-      </c>
-      <c r="F32" s="220">
-        <v>5</v>
-      </c>
-      <c r="G32" s="220">
-        <v>6</v>
-      </c>
-      <c r="H32" s="220">
-        <v>7</v>
-      </c>
-      <c r="I32" s="220">
-        <v>7</v>
-      </c>
-      <c r="J32" s="82"/>
-      <c r="K32" s="82"/>
-      <c r="L32" s="82"/>
-      <c r="M32" s="82"/>
-      <c r="N32" s="82"/>
     </row>
     <row r="33" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B33" s="82" t="s">
+        <v>194</v>
+      </c>
+      <c r="C33" s="82">
+        <v>2</v>
+      </c>
+      <c r="D33" s="82">
+        <v>2</v>
+      </c>
+      <c r="E33" s="82">
+        <v>2</v>
+      </c>
+      <c r="F33" s="82">
+        <v>3</v>
+      </c>
+      <c r="G33" s="82">
+        <v>3</v>
+      </c>
+      <c r="H33" s="82">
+        <v>3</v>
+      </c>
+      <c r="I33" s="82">
+        <v>3</v>
+      </c>
+      <c r="J33" s="82">
+        <v>3</v>
+      </c>
+      <c r="K33" s="82">
+        <v>3</v>
+      </c>
+      <c r="L33" s="82">
+        <v>3</v>
+      </c>
+      <c r="M33" s="82">
+        <v>3</v>
+      </c>
+      <c r="N33" s="82">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B34" s="82" t="s">
+        <v>197</v>
+      </c>
+      <c r="C34" s="220">
+        <v>9</v>
+      </c>
+      <c r="D34" s="220">
+        <v>10</v>
+      </c>
+      <c r="E34" s="220">
+        <v>11</v>
+      </c>
+      <c r="F34" s="220">
+        <v>12</v>
+      </c>
+      <c r="G34" s="220">
+        <v>13</v>
+      </c>
+      <c r="H34" s="82"/>
+      <c r="I34" s="82"/>
+      <c r="J34" s="82"/>
+      <c r="K34" s="82"/>
+      <c r="L34" s="82"/>
+      <c r="M34" s="82"/>
+      <c r="N34" s="82"/>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B35" s="82" t="s">
+        <v>238</v>
+      </c>
+      <c r="C35" s="220">
+        <v>2</v>
+      </c>
+      <c r="D35" s="220">
+        <v>3</v>
+      </c>
+      <c r="E35" s="220">
+        <v>3</v>
+      </c>
+      <c r="F35" s="220">
+        <v>5</v>
+      </c>
+      <c r="G35" s="220">
+        <v>6</v>
+      </c>
+      <c r="H35" s="220">
+        <v>7</v>
+      </c>
+      <c r="I35" s="220">
+        <v>7</v>
+      </c>
+      <c r="J35" s="82"/>
+      <c r="K35" s="82"/>
+      <c r="L35" s="82"/>
+      <c r="M35" s="82"/>
+      <c r="N35" s="82"/>
+    </row>
+    <row r="36" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B36" s="82" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="51" cm="1">
-        <f t="array" ref="C33:H33">TRANSPOSE(BIHAR!AA12:AA17)</f>
+      <c r="C36" s="51" cm="1">
+        <f t="array" ref="C36:H36">TRANSPOSE(BIHAR!AA12:AA17)</f>
         <v>626</v>
       </c>
-      <c r="D33" s="51">
+      <c r="D36" s="51">
         <v>618</v>
       </c>
-      <c r="E33" s="51">
+      <c r="E36" s="51">
         <v>692</v>
       </c>
-      <c r="F33" s="51">
+      <c r="F36" s="51">
         <v>894</v>
       </c>
-      <c r="G33" s="51">
+      <c r="G36" s="51">
         <v>1038</v>
       </c>
-      <c r="H33" s="51">
+      <c r="H36" s="51">
         <v>1464</v>
       </c>
-      <c r="I33" s="51">
+      <c r="I36" s="51">
         <f>1602+342+205</f>
         <v>2149</v>
       </c>
-      <c r="J33" s="51"/>
-      <c r="K33" s="51"/>
-      <c r="L33" s="51"/>
-      <c r="M33" s="51"/>
-      <c r="N33" s="51"/>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B34" s="82" t="s">
+      <c r="J36" s="51"/>
+      <c r="K36" s="51"/>
+      <c r="L36" s="51"/>
+      <c r="M36" s="51"/>
+      <c r="N36" s="51"/>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B37" s="82" t="s">
         <v>198</v>
       </c>
-      <c r="C34" s="51" cm="1">
-        <f t="array" ref="C34:H34">TRANSPOSE(F7:F12)</f>
+      <c r="C37" s="51" cm="1">
+        <f t="array" ref="C37:H37">TRANSPOSE(F10:F15)</f>
         <v>135465.839595992</v>
       </c>
-      <c r="D34" s="51">
+      <c r="D37" s="51">
         <v>165159.66833336878</v>
       </c>
-      <c r="E34" s="51">
+      <c r="E37" s="51">
         <v>198247.30981053683</v>
       </c>
-      <c r="F34" s="51">
+      <c r="F37" s="51">
         <v>225781.01373336388</v>
       </c>
-      <c r="G34" s="51">
+      <c r="G37" s="51">
         <v>254579.19335621063</v>
       </c>
-      <c r="H34" s="51">
+      <c r="H37" s="51">
         <v>332187.89644916437</v>
       </c>
-      <c r="I34" s="51">
+      <c r="I37" s="51">
         <v>502540.46866056195</v>
       </c>
-      <c r="J34" s="51">
+      <c r="J37" s="51">
         <v>569954</v>
       </c>
-      <c r="K34" s="51">
+      <c r="K37" s="51">
         <v>669365</v>
       </c>
-      <c r="L34" s="51">
+      <c r="L37" s="51">
         <v>790154</v>
       </c>
-      <c r="M34" s="51">
+      <c r="M37" s="51">
         <v>934694</v>
       </c>
-      <c r="N34" s="51">
+      <c r="N37" s="51">
         <v>1094380</v>
       </c>
     </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B35" s="82" t="s">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B38" s="82" t="s">
         <v>196</v>
       </c>
-      <c r="C35" s="51">
+      <c r="C38" s="51">
         <v>16080.571428571428</v>
       </c>
-      <c r="D35" s="51">
+      <c r="D38" s="51">
         <v>14920.417582417584</v>
       </c>
-      <c r="E35" s="51">
+      <c r="E38" s="51">
         <v>16544.270834894734</v>
       </c>
-      <c r="F35" s="182">
+      <c r="F38" s="182">
         <v>23508.117860161816</v>
       </c>
-      <c r="G35" s="182">
+      <c r="G38" s="182">
         <v>25532.329670329669</v>
       </c>
-      <c r="H35" s="182">
+      <c r="H38" s="182">
         <v>25532.329670329669</v>
       </c>
-      <c r="I35" s="182">
+      <c r="I38" s="182">
         <v>25532.329670329669</v>
       </c>
-      <c r="J35" s="182"/>
-      <c r="K35" s="182"/>
-      <c r="L35" s="52"/>
-      <c r="M35" s="52"/>
-      <c r="N35" s="52"/>
-    </row>
-    <row r="36" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="Q36" s="219"/>
-      <c r="R36" s="219"/>
-      <c r="S36" s="219"/>
-      <c r="T36" s="219"/>
-      <c r="U36" s="219"/>
+      <c r="J38" s="182"/>
+      <c r="K38" s="182"/>
+      <c r="L38" s="52"/>
+      <c r="M38" s="52"/>
+      <c r="N38" s="52"/>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="Q39" s="219"/>
+      <c r="R39" s="219"/>
+      <c r="S39" s="219"/>
+      <c r="T39" s="219"/>
+      <c r="U39" s="219"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
@@ -21738,19 +21855,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="225" t="s">
+      <c r="B2" s="232" t="s">
         <v>112</v>
       </c>
-      <c r="C2" s="225"/>
-      <c r="D2" s="225"/>
-      <c r="E2" s="225"/>
-      <c r="F2" s="225"/>
-      <c r="G2" s="225"/>
-      <c r="H2" s="225"/>
-      <c r="I2" s="225"/>
+      <c r="C2" s="232"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
+      <c r="G2" s="232"/>
+      <c r="H2" s="232"/>
+      <c r="I2" s="232"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="224" t="s">
+      <c r="B3" s="231" t="s">
         <v>84</v>
       </c>
       <c r="C3" s="105" t="s">
@@ -21759,20 +21876,20 @@
       <c r="D3" s="105" t="s">
         <v>52</v>
       </c>
-      <c r="E3" s="224" t="s">
+      <c r="E3" s="231" t="s">
         <v>189</v>
       </c>
-      <c r="F3" s="224"/>
-      <c r="G3" s="224" t="s">
+      <c r="F3" s="231"/>
+      <c r="G3" s="231" t="s">
         <v>190</v>
       </c>
-      <c r="H3" s="224"/>
+      <c r="H3" s="231"/>
       <c r="I3" s="105" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B4" s="224"/>
+      <c r="B4" s="231"/>
       <c r="C4" s="105" t="s">
         <v>93</v>
       </c>
@@ -21991,19 +22108,19 @@
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="225" t="s">
+      <c r="B16" s="232" t="s">
         <v>114</v>
       </c>
-      <c r="C16" s="225"/>
-      <c r="D16" s="225"/>
-      <c r="E16" s="225"/>
-      <c r="F16" s="225"/>
-      <c r="G16" s="225"/>
-      <c r="H16" s="225"/>
-      <c r="I16" s="225"/>
+      <c r="C16" s="232"/>
+      <c r="D16" s="232"/>
+      <c r="E16" s="232"/>
+      <c r="F16" s="232"/>
+      <c r="G16" s="232"/>
+      <c r="H16" s="232"/>
+      <c r="I16" s="232"/>
     </row>
     <row r="17" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="224" t="s">
+      <c r="B17" s="231" t="s">
         <v>84</v>
       </c>
       <c r="C17" s="105" t="s">
@@ -22012,20 +22129,20 @@
       <c r="D17" s="105" t="s">
         <v>52</v>
       </c>
-      <c r="E17" s="224" t="s">
+      <c r="E17" s="231" t="s">
         <v>189</v>
       </c>
-      <c r="F17" s="224"/>
-      <c r="G17" s="224" t="s">
+      <c r="F17" s="231"/>
+      <c r="G17" s="231" t="s">
         <v>190</v>
       </c>
-      <c r="H17" s="224"/>
+      <c r="H17" s="231"/>
       <c r="I17" s="105" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="224"/>
+      <c r="B18" s="231"/>
       <c r="C18" s="105" t="s">
         <v>93</v>
       </c>
@@ -22180,17 +22297,17 @@
       </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B26" s="225" t="s">
+      <c r="B26" s="232" t="s">
         <v>113</v>
       </c>
-      <c r="C26" s="225"/>
-      <c r="D26" s="225"/>
-      <c r="E26" s="225"/>
-      <c r="F26" s="225"/>
-      <c r="G26" s="225"/>
+      <c r="C26" s="232"/>
+      <c r="D26" s="232"/>
+      <c r="E26" s="232"/>
+      <c r="F26" s="232"/>
+      <c r="G26" s="232"/>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B27" s="224" t="s">
+      <c r="B27" s="231" t="s">
         <v>84</v>
       </c>
       <c r="C27" s="105" t="s">
@@ -22208,7 +22325,7 @@
       <c r="G27" s="105"/>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B28" s="224"/>
+      <c r="B28" s="231"/>
       <c r="C28" s="105" t="s">
         <v>61</v>
       </c>
@@ -22327,43 +22444,43 @@
     </row>
     <row r="35" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="36" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="226" t="s">
+      <c r="B36" s="223" t="s">
         <v>50</v>
       </c>
-      <c r="C36" s="227"/>
-      <c r="D36" s="227"/>
-      <c r="E36" s="227"/>
-      <c r="F36" s="227"/>
-      <c r="G36" s="227"/>
-      <c r="H36" s="227"/>
-      <c r="I36" s="227"/>
-      <c r="J36" s="228"/>
+      <c r="C36" s="224"/>
+      <c r="D36" s="224"/>
+      <c r="E36" s="224"/>
+      <c r="F36" s="224"/>
+      <c r="G36" s="224"/>
+      <c r="H36" s="224"/>
+      <c r="I36" s="224"/>
+      <c r="J36" s="225"/>
     </row>
     <row r="37" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="229" t="s">
+      <c r="B37" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="C37" s="229" t="s">
+      <c r="C37" s="226" t="s">
         <v>116</v>
       </c>
-      <c r="D37" s="229" t="s">
+      <c r="D37" s="226" t="s">
         <v>117</v>
       </c>
       <c r="E37" s="65" t="s">
         <v>97</v>
       </c>
-      <c r="F37" s="231" t="s">
+      <c r="F37" s="228" t="s">
         <v>118</v>
       </c>
-      <c r="G37" s="232"/>
-      <c r="H37" s="232"/>
-      <c r="I37" s="232"/>
-      <c r="J37" s="233"/>
+      <c r="G37" s="229"/>
+      <c r="H37" s="229"/>
+      <c r="I37" s="229"/>
+      <c r="J37" s="230"/>
     </row>
     <row r="38" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="230"/>
-      <c r="C38" s="230"/>
-      <c r="D38" s="230"/>
+      <c r="B38" s="227"/>
+      <c r="C38" s="227"/>
+      <c r="D38" s="227"/>
       <c r="E38" s="66" t="s">
         <v>60</v>
       </c>
@@ -22527,11 +22644,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B36:J36"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="F37:J37"/>
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B16:I16"/>
@@ -22542,6 +22654,11 @@
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="G17:H17"/>
+    <mergeCell ref="B36:J36"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="F37:J37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -22561,15 +22678,15 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="234" t="s">
+      <c r="B3" s="233" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="234"/>
-      <c r="D3" s="234"/>
-      <c r="E3" s="234"/>
-      <c r="F3" s="234"/>
-      <c r="G3" s="234"/>
-      <c r="H3" s="234"/>
+      <c r="C3" s="233"/>
+      <c r="D3" s="233"/>
+      <c r="E3" s="233"/>
+      <c r="F3" s="233"/>
+      <c r="G3" s="233"/>
+      <c r="H3" s="233"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="87"/>
@@ -22871,11 +22988,11 @@
       </c>
     </row>
     <row r="22" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="236" t="s">
+      <c r="B22" s="235" t="s">
         <v>103</v>
       </c>
-      <c r="C22" s="237"/>
-      <c r="D22" s="238"/>
+      <c r="C22" s="236"/>
+      <c r="D22" s="237"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="96" t="s">
@@ -22928,11 +23045,11 @@
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="235" t="s">
+      <c r="B30" s="234" t="s">
         <v>106</v>
       </c>
-      <c r="C30" s="235"/>
-      <c r="D30" s="235"/>
+      <c r="C30" s="234"/>
+      <c r="D30" s="234"/>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="99" t="s">
@@ -22998,11 +23115,11 @@
       </c>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B44" s="222" t="s">
+      <c r="B44" s="221" t="s">
         <v>79</v>
       </c>
-      <c r="C44" s="222"/>
-      <c r="D44" s="222"/>
+      <c r="C44" s="221"/>
+      <c r="D44" s="221"/>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45" s="99" t="s">
@@ -26212,13 +26329,13 @@
         <f t="shared" si="4"/>
         <v>355.29589041095892</v>
       </c>
-      <c r="W10" s="221" t="s">
+      <c r="W10" s="238" t="s">
         <v>216</v>
       </c>
-      <c r="X10" s="221"/>
-      <c r="Y10" s="221"/>
-      <c r="Z10" s="221"/>
-      <c r="AA10" s="221"/>
+      <c r="X10" s="238"/>
+      <c r="Y10" s="238"/>
+      <c r="Z10" s="238"/>
+      <c r="AA10" s="238"/>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
@@ -42000,32 +42117,32 @@
       </c>
     </row>
     <row r="3" spans="3:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="255" t="s">
         <v>119</v>
       </c>
-      <c r="D3" s="241"/>
-      <c r="E3" s="241"/>
-      <c r="F3" s="241"/>
-      <c r="G3" s="241"/>
-      <c r="H3" s="241"/>
-      <c r="I3" s="241"/>
-      <c r="J3" s="241"/>
-      <c r="K3" s="242"/>
+      <c r="D3" s="256"/>
+      <c r="E3" s="256"/>
+      <c r="F3" s="256"/>
+      <c r="G3" s="256"/>
+      <c r="H3" s="256"/>
+      <c r="I3" s="256"/>
+      <c r="J3" s="256"/>
+      <c r="K3" s="257"/>
       <c r="L3" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="4" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C4" s="243" t="s">
+      <c r="C4" s="258" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="243" t="s">
+      <c r="D4" s="258" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="243" t="s">
+      <c r="E4" s="258" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="243" t="s">
+      <c r="F4" s="258" t="s">
         <v>83</v>
       </c>
       <c r="G4" s="111" t="s">
@@ -42040,15 +42157,15 @@
       <c r="J4" s="112" t="s">
         <v>121</v>
       </c>
-      <c r="K4" s="243" t="s">
+      <c r="K4" s="258" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="5" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="244"/>
-      <c r="D5" s="245"/>
-      <c r="E5" s="244"/>
-      <c r="F5" s="244"/>
+      <c r="C5" s="259"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="259"/>
+      <c r="F5" s="259"/>
       <c r="G5" s="111" t="s">
         <v>53</v>
       </c>
@@ -42061,7 +42178,7 @@
       <c r="J5" s="113" t="s">
         <v>125</v>
       </c>
-      <c r="K5" s="244"/>
+      <c r="K5" s="259"/>
     </row>
     <row r="6" spans="3:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C6" s="114">
@@ -42217,11 +42334,11 @@
       </c>
     </row>
     <row r="13" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="249" t="s">
+      <c r="C13" s="243" t="s">
         <v>126</v>
       </c>
-      <c r="D13" s="250"/>
-      <c r="E13" s="251"/>
+      <c r="D13" s="244"/>
+      <c r="E13" s="245"/>
     </row>
     <row r="14" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C14" s="96" t="s">
@@ -42249,11 +42366,11 @@
       </c>
     </row>
     <row r="16" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="L16" s="252" t="s">
+      <c r="L16" s="246" t="s">
         <v>128</v>
       </c>
-      <c r="M16" s="252"/>
-      <c r="N16" s="252"/>
+      <c r="M16" s="246"/>
+      <c r="N16" s="246"/>
     </row>
     <row r="17" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
@@ -42463,38 +42580,38 @@
       <c r="C25" s="125"/>
     </row>
     <row r="26" spans="3:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="253" t="s">
+      <c r="C26" s="247" t="s">
         <v>134</v>
       </c>
-      <c r="D26" s="253" t="s">
+      <c r="D26" s="247" t="s">
         <v>135</v>
       </c>
-      <c r="E26" s="253" t="s">
+      <c r="E26" s="247" t="s">
         <v>136</v>
       </c>
-      <c r="F26" s="255" t="s">
+      <c r="F26" s="249" t="s">
         <v>137</v>
       </c>
       <c r="G26" s="126" t="s">
         <v>49</v>
       </c>
-      <c r="H26" s="256" t="s">
+      <c r="H26" s="250" t="s">
         <v>136</v>
       </c>
-      <c r="I26" s="256"/>
-      <c r="J26" s="256"/>
-      <c r="K26" s="257" t="s">
+      <c r="I26" s="250"/>
+      <c r="J26" s="250"/>
+      <c r="K26" s="251" t="s">
         <v>52</v>
       </c>
-      <c r="L26" s="259" t="s">
+      <c r="L26" s="253" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="27" spans="3:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C27" s="254"/>
-      <c r="D27" s="254"/>
-      <c r="E27" s="254"/>
-      <c r="F27" s="254"/>
+      <c r="C27" s="248"/>
+      <c r="D27" s="248"/>
+      <c r="E27" s="248"/>
+      <c r="F27" s="248"/>
       <c r="G27" s="127">
         <v>45627</v>
       </c>
@@ -42507,8 +42624,8 @@
       <c r="J27" s="129">
         <v>45717</v>
       </c>
-      <c r="K27" s="258"/>
-      <c r="L27" s="260"/>
+      <c r="K27" s="252"/>
+      <c r="L27" s="254"/>
     </row>
     <row r="28" spans="3:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28" s="130" t="s">
@@ -42645,20 +42762,20 @@
       </c>
     </row>
     <row r="36" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="C36" s="246" t="s">
+      <c r="C36" s="240" t="s">
         <v>141</v>
       </c>
-      <c r="D36" s="247"/>
-      <c r="E36" s="247"/>
-      <c r="F36" s="247"/>
-      <c r="G36" s="247"/>
-      <c r="H36" s="247"/>
-      <c r="I36" s="247"/>
-      <c r="J36" s="247"/>
-      <c r="K36" s="247"/>
-      <c r="L36" s="247"/>
-      <c r="M36" s="247"/>
-      <c r="N36" s="248"/>
+      <c r="D36" s="241"/>
+      <c r="E36" s="241"/>
+      <c r="F36" s="241"/>
+      <c r="G36" s="241"/>
+      <c r="H36" s="241"/>
+      <c r="I36" s="241"/>
+      <c r="J36" s="241"/>
+      <c r="K36" s="241"/>
+      <c r="L36" s="241"/>
+      <c r="M36" s="241"/>
+      <c r="N36" s="242"/>
     </row>
     <row r="37" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C37" s="137" t="s">
@@ -42928,6 +43045,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C3:K3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="K4:K5"/>
     <mergeCell ref="C36:N36"/>
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="L16:N16"/>
@@ -42938,12 +43061,6 @@
     <mergeCell ref="H26:J26"/>
     <mergeCell ref="K26:K27"/>
     <mergeCell ref="L26:L27"/>
-    <mergeCell ref="C3:K3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="K4:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
